--- a/evidencias/Pruebas_Unitarias_RideU.xlsx
+++ b/evidencias/Pruebas_Unitarias_RideU.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Inventario de pruebas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Casos de ajuste (7)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Detalle evidencias" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cobertura" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Guía de lectura" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Casos de ajuste (21)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Criterios vs pruebas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Detalle evidencias" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cobertura" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ubicación de tests" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Guía de lectura" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,14 +102,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -122,6 +124,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -489,11 +494,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -503,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RideU — Evidencia de Pruebas Unitarias</t>
+          <t>RideU — Evidencia de Pruebas Unitarias (21 casos de ajuste)</t>
         </is>
       </c>
     </row>
@@ -550,8 +555,10 @@
           <t>Total pruebas unitarias</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>61</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>66+ (ver Inventario)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -560,8 +567,10 @@
           <t>Casos de ajuste documentados</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>7</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -584,7 +593,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>61 passed / 0 failed</t>
+          <t>Todos los tests en verde tras correcciones</t>
         </is>
       </c>
     </row>
@@ -596,30 +605,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 15:04 (America/Bogota)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+          <t>2026-10-27 15:52 (America/Bogota)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mapa de archivos de test</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>evidencias/MAPA_PRUEBAS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Las pruebas unitarias NO tocan PostgreSQL real ni red: se mockean pool, bcrypt y correo. Los 7 casos de ajuste muestran el ciclo defecto → fallo del test → corrección → test en verde. Evidencias en carpeta evidencias/casos-ajuste/CU-0X/.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Las pruebas unitarias NO tocan PostgreSQL real ni red. Los 21 casos de ajuste muestran el ciclo defecto → fallo del test → corrección → test en verde. Evidencias en evidencias/casos-ajuste/CU-XX/. Las funciones de test están en backend/tests/ (ver MAPA_PRUEBAS.md).</t>
+        </is>
+      </c>
+    </row>
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
+    <row r="17"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B12:F16"/>
+    <mergeCell ref="B13:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -637,12 +658,12 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
@@ -697,7 +718,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Caso feliz + dominio inválido + evil.com</t>
+          <t>Dominio inválido + evil.com</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -724,12 +745,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Campos vacíos/nulos y longitudes</t>
+          <t>Campos vacíos/nulos y body inválido</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Rechazo 400 lógico (ok=false)</t>
+          <t>ok=false; error campo body</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -756,7 +777,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Contraseña 8-72 y WhatsApp CO</t>
+          <t>Nombre 3-120, contraseña 8-72, WhatsApp CO</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -852,7 +873,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Crear y buscar sesión opaca</t>
+          <t>Crear y buscar sesión (7 días)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -980,7 +1001,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>POST login 200/400/401/403</t>
+          <t>POST login 200/400/401/403 + normalización correo</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1012,7 +1033,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Bearer obligatorio</t>
+          <t>Bearer obligatorio; rechaza Basic</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1069,20 +1090,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -1098,51 +1121,61 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Qué se probó</t>
+          <t>Criterio de aceptación</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Qué se probó (test)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Archivo de prueba</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Resultado esperado</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Resultado obtenido (error)</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Inconformidad</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Ajuste realizado</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Evidencia del fallo</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Evidencia de resolución</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Extracto Jest (Expected/Received)</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Extracto Jest</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Estado final</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="55" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CU-01</t>
@@ -1155,51 +1188,61 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Rechazo de correo que solo contiene unicauca.edu.co como subcadena</t>
+          <t>Solo correos que terminen exactamente en @unicauca.edu.co</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
+          <t>debería rechazar un correo que solo contiene unicauca.edu.co como subcadena</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>ok=false; error en campo correo</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>ok=true (regex sin anclas aceptaba ana@unicauca.edu.co.evil.com)</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Regex permisiva /unicauca\.edu\.co/i sin ^ $</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Se restauró /^[^\s@]+@unicauca\.edu\.co$/</t>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>ok=true (evil.com aceptado)</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
+          <t>Aceptaba ana@unicauca.edu.co.evil.com</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Anclar la regex a ^[^\s@]+@unicauca\.edu\.co$</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-01/01_fallo.log</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-01/02_exito.log</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>Expected: false | Received: true</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería rechazar un correo que solo contiene unicauca.edu.co como subcadena | Expected: false | Received: true</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="55" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CU-02</t>
@@ -1212,51 +1255,61 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Registro con correo ya existente</t>
+          <t>Correo ya registrado → HTTP 409 Conflict</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>debería responder 409 si el correo ya existe</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>HTTP 409 Conflict</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Código de estado incorrecto para duplicado</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>return res.status(409) cuando buscarPorCorreo encuentra cuenta</t>
-        </is>
-      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
+          <t>Devolvía 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Usar status 409 cuando el correo existe</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-02/01_fallo.log</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-02/02_exito.log</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 409 | Received: 400</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>● authController.registrar › debería responder 409 si el correo ya existe | Expected: 409 | Received: 400</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CU-03</t>
@@ -1269,51 +1322,61 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Login con cuenta Sin verificar</t>
+          <t>Cuenta Sin verificar → HTTP 403 + EMAIL_NOT_VERIFIED</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>HTTP 403 + codigo EMAIL_NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 401 (confundía con credenciales inválidas)</t>
+          <t>debería responder 403 si el correo no está verificado</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Semántica de autorización incorrecta</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Devolver 403 Forbidden con mensaje de verificación</t>
+          <t>HTTP 403 + EMAIL_NOT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 401</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
+          <t>Se confundía con credenciales inválidas (401)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Devolver 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-03/01_fallo.log</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-03/02_exito.log</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 403 | Received: 401</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>● authController.iniciarSesion › debería responder 403 si el correo no está verificado | Expected: 403 | Received: 401</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CU-04</t>
@@ -1326,51 +1389,61 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>GET /sesion sin encabezado Authorization Bearer</t>
+          <t>Sin Authorization Bearer → HTTP 401</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>debería responder 401 si no hay encabezado Authorization Bearer</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>HTTP 401 Unauthorized</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Falta de autenticación reportada como error de validación</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Responder 401 Debes iniciar sesión</t>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 400</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
+          <t>Falta de auth reportada como 400</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Responder 401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-04/01_fallo.log</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-04/02_exito.log</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 401 | Received: 400</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>● middleware requiereSesion › debería responder 401 si no hay encabezado Authorization Bearer | Expected: 401 | Received: 400</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="55" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CU-05</t>
@@ -1383,51 +1456,61 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Normalización de WhatsApp colombiano</t>
+          <t>Celular CO válido se guarda como +573XXXXXXXXX</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>whatsapp = +573001234567</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>whatsapp = 3001234567 (sin +57)</t>
+          <t>debería normalizar WhatsApp con prefijo 57 a formato \+57</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Incumplía constraint SQL ^\+57[3][0-9]{9}$</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>return `+57${local}` tras validar 10 dígitos</t>
+          <t>whatsapp=+573001234567</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>sin prefijo +57</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
+          <t>Se guardaba sin prefijo internacional</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Prefijar +57 tras validar 10 dígitos</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-05/01_fallo.log</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-05/02_exito.log</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Expected: "+573001234567" | Received: "3001234567"</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería normalizar WhatsApp con prefijo 57 a formato +57 | Expected: "+573001234567" | Received: "3001234567"</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55" customHeight="1">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CU-06</t>
@@ -1440,51 +1523,61 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Verificación con token expirado</t>
+          <t>Token vencido → HTTP 400</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>HTTP 400 + mensaje de expiración</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 Not Found</t>
+          <t>debería responder 400 si el enlace expiró</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Token vencido tratado como recurso inexistente</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>status(400) con 'El enlace de verificación expiró.'</t>
+          <t>HTTP 400 expiró</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
+          <t>Respondía 404 Not Found</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>status(400) con mensaje de expiración</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-06/01_fallo.log</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-06/02_exito.log</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 400 | Received: 404</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>● authController.verificar › debería responder 400 si el enlace expiró | Expected: 400 | Received: 404</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="55" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CU-07</t>
@@ -1497,45 +1590,993 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Login con correo/contraseña vacíos</t>
+          <t>Correo/contraseña vacíos → HTTP 400</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 401 Unauthorized</t>
+          <t>debería responder 400 si faltan correo o contraseña</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Validación de obligatoriedad mezclada con auth fallida</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Validar presencia antes de consultar BD y responder 400</t>
+          <t>HTTP 400 campos vacíos</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 401</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
+          <t>Respondía 401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Validar presencia y responder 400</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-07/01_fallo.log</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-07/02_exito.log</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 400 | Received: 401</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>● authController.iniciarSesion › debería responder 400 si faltan correo o contraseña | Expected: 400 | Received: 401</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>validation/registro.js</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Contraseña con longitud &lt; 8 → ok=false</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar una contraseña de exactamente 7 caracteres</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>ok=false contraseña 7 chars</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>ok=true (sin mínimo)</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Se omitió la validación de longitud mínima</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Rechazar si contrasena.length &lt; 8</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-08/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-08/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería rechazar una contraseña de exactamente 7 caracteres | Expected: false | Received: true</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>validation/registro.js</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Nombre con longitud &lt; 3 → error en campo nombre</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar un nombre de exactamente 2 caracteres</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>error campo nombre (2 chars)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>nombre aceptado</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>No se validaba el mínimo de 3 caracteres</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Rechazar si nombre.length &lt; 3 || &gt; 120</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-09/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-09/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería rechazar un nombre de exactamente 2 caracteres | Expected: false | Received: true</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CU-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>controllers/authController.js</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>motivo usado → HTTP 409 Conflict</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 409 si el enlace ya fue usado</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 409 enlace usado</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 400</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Respondía 400 en lugar de conflicto</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>status(409) cuando motivo === 'usado'</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-10/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-10/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>● authController.verificar › debería responder 409 si el enlace ya fue usado | Expected: 409 | Received: 400</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CU-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>controllers/authController.js</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Credenciales inválidas → HTTP 401 genérico</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si la contraseña no coincide</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 401 credenciales</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Respondía 404 Not Found</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>status(401) con mensaje genérico</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-11/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-11/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>● authController.iniciarSesion › debería responder 401 si la contraseña no coincide | Expected: 401 | Received: 404</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CU-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>middleware/requiereSesion.js</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Token de sesión inválido/expirado → HTTP 401</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si el token de sesión no es válido</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 401 sesión inválida</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 403</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Respondía 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>status(401) Tu sesión no es válida o expiró</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-12/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-12/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>● middleware requiereSesion › debería responder 401 si el token de sesión no es válido | Expected: 401 | Received: 403</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CU-13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>controllers/authController.js</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Alta de cuenta → HTTP 201 Created</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>POST /registro debería usar código 201 y no 200 en el alta exitosa</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>tests/routes/authRoutes.test.js</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 201 Created</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Respondía 200 OK</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>status(201) tras crear usuario y enviar correo</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-13/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-13/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>● rutas /api/auth (Supertest) › POST /registro debería usar código 201 y no 200 en el alta exitosa | Expected: 201 | Received: 200</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>CU-14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>services/correo.js</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>URL base sin // duplicado antes de /registro/verificacion</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>debería armar el enlace de verificación sin barra final duplicada</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>tests/services/correo.test.js</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>URL sin // duplicado</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>…5173//registro…</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Quedaba http://host:5173//registro/...</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Quitar barra final con replace(/\/$/, '')</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-14/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-14/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>● servicio correo › debería armar el enlace de verificación sin barra final duplicada | Expected: "http://localhost:5173/registro/verificacion?token=abc123" | Received: "http://localhost:5173//registro/verificacion?token=abc123"</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CU-15</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>models/usuario.js</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>hashToken produce hex de 64 caracteres (SHA-256)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>debería hashear el token con SHA-256 en hexadecimal</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>tests/models/usuario.test.js</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>hash hex 64 (SHA-256)</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>hash hex 40 (SHA-1)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>SHA-1 produce 40 caracteres; rompe sesiones/verificación</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>createHash('sha256')</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-15/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-15/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>● modelo usuario › debería hashear el token con SHA-256 en hexadecimal | Expected pattern: /^[a-f0-9]{64}$/ | Received string:  "a9993e364706816aba3e25717850c26c9cd0d89d"</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CU-16</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>controllers/authController.js</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>El correo se busca siempre en minúsculas</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>debería normalizar el correo a minúsculas antes de buscar credenciales</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>búsqueda en minúsculas</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>correo sin toLowerCase</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Ana@Unicauca.edu.co no coincidía con ana@...</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>trim().toLowerCase() antes de buscarCredencialesPorCorreo</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-16/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-16/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>● authController.iniciarSesion › debería normalizar el correo a minúsculas antes de buscar credenciales | Expected: "ana.perez@unicauca.edu.co" | Received: "Ana.Perez@Unicauca.edu.co"</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CU-17</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>validation/registro.js</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Solo celulares colombianos que empiecen por 3 (10 dígitos)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar WhatsApp que no sea celular colombiano</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>rechazar fijo 6…</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>6012345678 aceptado</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Aceptaba 6012345678</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Validar con /^3\d{9}$/</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-17/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-17/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería rechazar WhatsApp que no sea celular colombiano | Expected: false | Received: true</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CU-18</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>services/correo.js</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>MAIL_MODE distinto de console|smtp → Error</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar un MAIL_MODE desconocido</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>tests/services/correo.test.js</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Error MAIL_MODE</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>no lanzaba error</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Continuaba como si fuera válido</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>throw new Error('MAIL_MODE debe ser console o smtp.')</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-18/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-18/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>● servicio correo › debería rechazar un MAIL_MODE desconocido | Received promise resolved instead of rejected</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CU-19</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>validation/registro.js</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>body null/array → ok=false con error de cuerpo</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar campos vacíos o nulos en el cuerpo</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>null → error campo body</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>TypeError / sin guarda</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Se omitía la guarda y fallaba de forma opaca</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Rechazar si body === null || no es objeto || es array</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-19/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-19/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería rechazar campos vacíos o nulos en el cuerpo</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>CU-20</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>middleware/requiereSesion.js</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Solo esquema Bearer es válido; Basic → 401</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar el esquema Basic y exigir Bearer</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Basic → 401 sin consultar</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Basic aceptado como sesión</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Authorization: Basic ... pasaba al buscador de sesión</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Exigir tipo === 'Bearer'</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-20/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-20/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>● middleware requiereSesion › debería rechazar el esquema Basic y exigir Bearer | Expected: 401 | Received: 0</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CU-21</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>models/sesion.js</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Duración de sesión = 7 días (168 horas)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>debería crear una sesión con token opaco y expiración a 7 días</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>tests/models/sesion.test.js</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>expira ≥ 6 días</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>expira en 1 hora</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>HORAS_SESION = 1</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>const HORAS_SESION = 24 * 7</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-21/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-21/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>● modelo sesion › debería crear una sesión con token opaco y expiración a 7 días | Expected: &gt; 1793652683731 | Received:   1793137883731</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
@@ -1552,13 +2593,628 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Criterio de aceptación</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Prueba unitaria asociada</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>CU-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Solo correos que terminen exactamente en @unicauca.edu.co</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar un correo que solo contiene unicauca.edu.co como subcadena</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>CU-02</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Correo ya registrado → HTTP 409 Conflict</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 409 si el correo ya existe</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CU-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta Sin verificar → HTTP 403 + EMAIL_NOT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 403 si el correo no está verificado</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CU-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Sin Authorization Bearer → HTTP 401</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si no hay encabezado Authorization Bearer</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CU-05</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Celular CO válido se guarda como +573XXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>debería normalizar WhatsApp con prefijo 57 a formato \+57</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CU-06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Token vencido → HTTP 400</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 400 si el enlace expiró</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CU-07</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Correo/contraseña vacíos → HTTP 400</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 400 si faltan correo o contraseña</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Contraseña con longitud &lt; 8 → ok=false</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar una contraseña de exactamente 7 caracteres</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Nombre con longitud &lt; 3 → error en campo nombre</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar un nombre de exactamente 2 caracteres</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CU-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>motivo usado → HTTP 409 Conflict</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 409 si el enlace ya fue usado</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CU-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Credenciales inválidas → HTTP 401 genérico</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si la contraseña no coincide</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CU-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Token de sesión inválido/expirado → HTTP 401</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si el token de sesión no es válido</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CU-13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Alta de cuenta → HTTP 201 Created</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>POST /registro debería usar código 201 y no 200 en el alta exitosa</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>tests/routes/authRoutes.test.js</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>CU-14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>URL base sin // duplicado antes de /registro/verificacion</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>debería armar el enlace de verificación sin barra final duplicada</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>tests/services/correo.test.js</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CU-15</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>hashToken produce hex de 64 caracteres (SHA-256)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>debería hashear el token con SHA-256 en hexadecimal</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>tests/models/usuario.test.js</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CU-16</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>El correo se busca siempre en minúsculas</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>debería normalizar el correo a minúsculas antes de buscar credenciales</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CU-17</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Solo celulares colombianos que empiecen por 3 (10 dígitos)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar WhatsApp que no sea celular colombiano</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CU-18</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>MAIL_MODE distinto de console|smtp → Error</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar un MAIL_MODE desconocido</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>tests/services/correo.test.js</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CU-19</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>body null/array → ok=false con error de cuerpo</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar campos vacíos o nulos en el cuerpo</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>CU-20</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Solo esquema Bearer es válido; Basic → 401</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar el esquema Basic y exigir Bearer</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CU-21</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Duración de sesión = 7 días (168 horas)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>debería crear una sesión con token opaco y expiración a 7 días</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>tests/models/sesion.test.js</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1608,7 +3264,7 @@
 expect(received).toBe(expected) // Object.is equality
 expect(resultado.ok).toBe(false);
 expect(resultado.errores[0].campo).toBe("correo");
-Tests:       1 failed, 7 skipped, 8 total
+Tests:       1 failed, 9 skipped, 10 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1631,7 +3287,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Tests:       7 skipped, 1 passed, 8 total
+          <t>Tests:       9 skipped, 1 passed, 10 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1661,7 +3317,7 @@
 expect(received).toBe(expected) // Object.is equality
 expect(res.statusCode).toBe(409);
 expect(res.cuerpo.mensaje).toMatch(/Ya existe/);
-Tests:       1 failed, 15 skipped, 16 total
+Tests:       1 failed, 16 skipped, 17 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1684,7 +3340,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Tests:       15 skipped, 1 passed, 16 total
+          <t>Tests:       16 skipped, 1 passed, 17 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1715,7 +3371,7 @@
 expect(res.statusCode).toBe(403);
 expect(res.cuerpo.codigo).toBe("EMAIL_NOT_VERIFIED");
 expect(crearSesion).not.toHaveBeenCalled();
-Tests:       1 failed, 15 skipped, 16 total
+Tests:       1 failed, 16 skipped, 17 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1738,7 +3394,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Tests:       15 skipped, 1 passed, 16 total
+          <t>Tests:       16 skipped, 1 passed, 17 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1769,7 +3425,7 @@
 expect(res.statusCode).toBe(401);
 expect(res.cuerpo.mensaje).toMatch(/iniciar sesión/);
 expect(next).not.toHaveBeenCalled();
-Tests:       1 failed, 3 skipped, 4 total
+Tests:       1 failed, 4 skipped, 5 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1792,7 +3448,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Tests:       3 skipped, 1 passed, 4 total
+          <t>Tests:       4 skipped, 1 passed, 5 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1822,7 +3478,7 @@
 expect(received).toBe(expected) // Object.is equality
 expect(resultado.ok).toBe(true);
 expect(resultado.datos.whatsapp).toBe("+573001234567");
-Tests:       1 failed, 7 skipped, 8 total
+Tests:       1 failed, 9 skipped, 10 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1845,7 +3501,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Tests:       7 skipped, 1 passed, 8 total
+          <t>Tests:       9 skipped, 1 passed, 10 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1875,7 +3531,7 @@
 expect(received).toBe(expected) // Object.is equality
 expect(res.statusCode).toBe(400);
 expect(res.cuerpo.mensaje).toMatch(/expiró/);
-Tests:       1 failed, 15 skipped, 16 total
+Tests:       1 failed, 16 skipped, 17 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1898,7 +3554,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Tests:       15 skipped, 1 passed, 16 total
+          <t>Tests:       16 skipped, 1 passed, 17 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1927,7 +3583,7 @@
 Received: 401
 expect(received).toBe(expected) // Object.is equality
 expect(res.statusCode).toBe(400);
-Tests:       1 failed, 15 skipped, 16 total
+Tests:       1 failed, 16 skipped, 17 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1950,7 +3606,743 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Tests:       15 skipped, 1 passed, 16 total
+          <t>Tests:       16 skipped, 1 passed, 17 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/validation/registro.test.js
+● validarRegistro › debería rechazar una contraseña de exactamente 7 caracteres
+Expected: false
+Received: true
+expect(received).toBe(expected) // Object.is equality
+expect(resultado.ok).toBe(false);
+expect(resultado.errores.some((e) =&gt; e.campo === "contrasena")).toBe(true);
+Tests:       1 failed, 9 skipped, 10 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       9 skipped, 1 passed, 10 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/validation/registro.test.js
+● validarRegistro › debería rechazar un nombre de exactamente 2 caracteres
+Expected: false
+Received: true
+expect(received).toBe(expected) // Object.is equality
+expect(resultado.ok).toBe(false);
+expect(resultado.errores[0].campo).toBe("nombre");
+Tests:       1 failed, 9 skipped, 10 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       9 skipped, 1 passed, 10 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CU-10</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/controllers/authController.test.js
+● authController.verificar › debería responder 409 si el enlace ya fue usado
+Expected: 409
+Received: 400
+expect(received).toBe(expected) // Object.is equality
+expect(res.statusCode).toBe(409);
+Tests:       1 failed, 16 skipped, 17 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>CU-10</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       16 skipped, 1 passed, 17 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CU-11</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/controllers/authController.test.js
+● authController.iniciarSesion › debería responder 401 si la contraseña no coincide
+Expected: 401
+Received: 404
+expect(received).toBe(expected) // Object.is equality
+expect(res.statusCode).toBe(401);
+expect(res.cuerpo.mensaje).toBe("Correo o contraseña incorrectos");
+expect(crearSesion).not.toHaveBeenCalled();
+Tests:       1 failed, 16 skipped, 17 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CU-11</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       16 skipped, 1 passed, 17 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>CU-12</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/middleware/requiereSesion.test.js
+● middleware requiereSesion › debería responder 401 si el token de sesión no es válido
+Expected: 401
+Received: 403
+expect(received).toBe(expected) // Object.is equality
+expect(res.statusCode).toBe(401);
+expect(res.cuerpo.mensaje).toMatch(/no es válida|expiró/);
+expect(next).not.toHaveBeenCalled();
+Tests:       1 failed, 4 skipped, 5 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>CU-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       4 skipped, 1 passed, 5 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CU-13</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/routes/authRoutes.test.js
+● rutas /api/auth (Supertest) › POST /registro debería usar código 201 y no 200 en el alta exitosa
+Expected: 201
+Received: 200
+expect(received).toBe(expected) // Object.is equality
+expect(respuesta.status).toBe(201);
+expect(respuesta.status).not.toBe(200);
+Tests:       1 failed, 10 skipped, 11 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>CU-13</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       10 skipped, 1 passed, 11 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>CU-14</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/services/correo.test.js
+● servicio correo › debería armar el enlace de verificación sin barra final duplicada
+Expected: "http://localhost:5173/registro/verificacion?token=abc123"
+Received: "http://localhost:5173//registro/verificacion?token=abc123"
+expect(received).toBe(expected) // Object.is equality
+expect(enlace).toBe("http://localhost:5173/registro/verificacion?token=abc123");
+Tests:       1 failed, 5 skipped, 6 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>CU-14</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       5 skipped, 1 passed, 6 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>CU-15</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/models/usuario.test.js
+● modelo usuario › debería hashear el token con SHA-256 en hexadecimal
+expect(received).toMatch(expected)
+expect(hash).toMatch(/^[a-f0-9]{64}$/);
+expect(hash).toBe(hashToken("abc"));
+expect(hash).not.toBe(hashToken("abd"));
+Tests:       1 failed, 9 skipped, 10 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CU-15</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       9 skipped, 1 passed, 10 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CU-16</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/controllers/authController.test.js
+● authController.iniciarSesion › debería normalizar el correo a minúsculas antes de buscar credenciales
+Expected: "ana.perez@unicauca.edu.co"
+Received: "Ana.Perez@Unicauca.edu.co"
+expect(jest.fn()).toHaveBeenCalledWith(...expected)
+expect(buscarCredencialesPorCorreo).toHaveBeenCalledWith("ana.perez@unicauca.edu.co");
+expect(res.statusCode).toBe(200);
+Tests:       1 failed, 16 skipped, 17 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CU-16</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       16 skipped, 1 passed, 17 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CU-17</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/validation/registro.test.js
+● validarRegistro › debería rechazar WhatsApp que no sea celular colombiano
+Expected: false
+Received: true
+expect(received).toBe(expected) // Object.is equality
+expect(resultado.ok).toBe(false);
+expect(resultado.errores[0].campo).toBe("whatsapp");
+expect(fijo.ok).toBe(false);
+Tests:       1 failed, 9 skipped, 10 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>CU-17</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       9 skipped, 1 passed, 10 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>CU-18</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/services/correo.test.js
+● servicio correo › debería rechazar un MAIL_MODE desconocido
+expect(received).rejects.toThrow()
+expect(
+Tests:       1 failed, 5 skipped, 6 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>CU-18</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       5 skipped, 1 passed, 6 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>CU-19</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/validation/registro.test.js
+● validarRegistro › debería rechazar campos vacíos o nulos en el cuerpo
+Tests:       1 failed, 9 skipped, 10 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>CU-19</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       9 skipped, 1 passed, 10 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>CU-20</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/middleware/requiereSesion.test.js
+● middleware requiereSesion › debería rechazar el esquema Basic y exigir Bearer
+Expected: 401
+Received: 0
+expect(received).toBe(expected) // Object.is equality
+expect(res.statusCode).toBe(401);
+expect(buscarUsuarioPorSesion).not.toHaveBeenCalled();
+expect(next).not.toHaveBeenCalled();
+Tests:       1 failed, 4 skipped, 5 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>CU-20</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       4 skipped, 1 passed, 5 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>CU-21</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/models/sesion.test.js
+● modelo sesion › debería crear una sesión con token opaco y expiración a 7 días
+Expected: &gt; 1793652683731
+Received:   1793137883731
+expect(received).toBeGreaterThan(expected)
+expect(token).toMatch(/^[a-f0-9]{64}$/);
+expect(expira.getTime()).toBeGreaterThan(antes + 6 * 24 * 60 * 60 * 1000);
+expect(query).toHaveBeenCalledWith(
+Tests:       1 failed, 2 skipped, 3 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CU-21</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       2 skipped, 1 passed, 3 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1960,7 +4352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2259,7 +4651,205 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Mapa rápido: dónde están las funciones de prueba</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Carpeta / archivo</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Qué contiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Carpeta raíz de la suite Jest (NO modificar producción desde aquí)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Tests de validarRegistro()</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/security/password.test.js</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Tests de hash/compare bcrypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/models/usuario.test.js</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Tests del modelo usuario (tokens, verificarCuenta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/models/sesion.test.js</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Tests del modelo sesión</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/services/correo.test.js</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tests de enlaceVerificacion / enviarCorreoVerificacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Tests de registrar / verificar / iniciarSesion / sesionActual</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Tests del middleware requiereSesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/routes/authRoutes.test.js</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Tests HTTP Supertest de /api/auth</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/helpers/http.js</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Helpers crearRespuestaMock y crearRequest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-XX/</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Evidencia fallo/éxito de cada caso de ajuste</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/Pruebas_Unitarias_RideU.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Este Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/MAPA_PRUEBAS.md</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Documentación ampliada del mapa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2268,7 +4858,7 @@
   <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2282,42 +4872,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Mostrar la hoja 'Inventario de pruebas': qué se probó en auth (validación, hash, tokens, controladores, rutas).</t>
+          <t>1. Hoja 'Inventario de pruebas': qué se probó en auth.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Abrir 'Casos de ajuste (7)': cada fila es un defecto detectado por un test unitario.</t>
+          <t>2. Hoja 'Casos de ajuste (21)': cada fila = defecto + criterio + test + evidencias.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. Para cada CU-0X, abrir evidencias/casos-ajuste/CU-0X/01_fallo.log (Expected vs Received) y 02_exito.log (PASS).</t>
+          <t>3. Hoja 'Criterios vs pruebas': trazabilidad criterio ↔ test.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. Mostrar cobertura final (&gt;=70% en lógica de negocio; global ~94% líneas).</t>
+          <t>4. Por cada CU-XX abrir evidencias/casos-ajuste/CU-XX/01_fallo.log y 02_exito.log.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. Comando de reproducción: cd backend &amp;&amp; npm test &amp;&amp; npm run test:coverage</t>
+          <t>5. Hoja 'Ubicación de tests' o MAPA_PRUEBAS.md: dónde están los archivos.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6. Las pruebas usan mocks: no requieren PostgreSQL ni SMTP reales.</t>
+          <t>6. Reproducir: cd backend &amp;&amp; npm test &amp;&amp; npm run test:coverage</t>
         </is>
       </c>
     </row>

--- a/evidencias/Pruebas_Unitarias_RideU.xlsx
+++ b/evidencias/Pruebas_Unitarias_RideU.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Inventario de pruebas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Casos de ajuste (7)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Detalle evidencias" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cobertura" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Guía de lectura" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Casos de ajuste (13)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Criterios vs pruebas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Detalle evidencias" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cobertura" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ubicación de tests" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Guía de lectura" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,14 +102,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -122,6 +124,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -489,11 +494,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -503,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RideU — Evidencia de Pruebas Unitarias</t>
+          <t>RideU — Evidencia de Pruebas Unitarias (13 casos de ajuste)</t>
         </is>
       </c>
     </row>
@@ -550,8 +555,10 @@
           <t>Total pruebas unitarias</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>61</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>66+ (ver Inventario)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -560,8 +567,10 @@
           <t>Casos de ajuste documentados</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>7</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -584,7 +593,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>61 passed / 0 failed</t>
+          <t>Todos los tests en verde tras correcciones</t>
         </is>
       </c>
     </row>
@@ -596,30 +605,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 15:04 (America/Bogota)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+          <t>2026-10-27 15:52 (America/Bogota)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mapa de archivos de test</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>evidencias/MAPA_PRUEBAS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Las pruebas unitarias NO tocan PostgreSQL real ni red: se mockean pool, bcrypt y correo. Los 7 casos de ajuste muestran el ciclo defecto → fallo del test → corrección → test en verde. Evidencias en carpeta evidencias/casos-ajuste/CU-0X/.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Las pruebas unitarias NO tocan PostgreSQL real ni red. Los 13 casos de ajuste muestran el ciclo defecto → fallo del test → corrección → test en verde. Evidencias en evidencias/casos-ajuste/CU-XX/. Las funciones de test están en backend/tests/ (ver MAPA_PRUEBAS.md).</t>
+        </is>
+      </c>
+    </row>
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
+    <row r="17"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B12:F16"/>
+    <mergeCell ref="B13:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -637,12 +658,12 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
@@ -697,7 +718,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Caso feliz + dominio inválido + evil.com</t>
+          <t>Dominio inválido + evil.com</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -724,12 +745,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Campos vacíos/nulos y longitudes</t>
+          <t>Campos vacíos/nulos y body inválido</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Rechazo 400 lógico (ok=false)</t>
+          <t>ok=false; error campo body</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -756,7 +777,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Contraseña 8-72 y WhatsApp CO</t>
+          <t>Nombre 3-120, contraseña 8-72, WhatsApp CO</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -852,7 +873,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Crear y buscar sesión opaca</t>
+          <t>Crear y buscar sesión (7 días)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -980,7 +1001,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>POST login 200/400/401/403</t>
+          <t>POST login 200/400/401/403 + normalización correo</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1012,7 +1033,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Bearer obligatorio</t>
+          <t>Bearer obligatorio; rechaza Basic</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1069,20 +1090,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -1098,51 +1121,61 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Qué se probó</t>
+          <t>Criterio de aceptación</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Qué se probó (test)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Archivo de prueba</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Resultado esperado</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Resultado obtenido (error)</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Inconformidad</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Ajuste realizado</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Evidencia del fallo</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Evidencia de resolución</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Extracto Jest (Expected/Received)</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Extracto Jest</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Estado final</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="55" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CU-01</t>
@@ -1155,51 +1188,61 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Rechazo de correo que solo contiene unicauca.edu.co como subcadena</t>
+          <t>Solo correos que terminen exactamente en @unicauca.edu.co</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
+          <t>debería rechazar un correo que solo contiene unicauca.edu.co como subcadena</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>ok=false; error en campo correo</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>ok=true (regex sin anclas aceptaba ana@unicauca.edu.co.evil.com)</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Regex permisiva /unicauca\.edu\.co/i sin ^ $</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Se restauró /^[^\s@]+@unicauca\.edu\.co$/</t>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>ok=true (evil.com aceptado)</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
+          <t>Aceptaba ana@unicauca.edu.co.evil.com</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Anclar la regex a ^[^\s@]+@unicauca\.edu\.co$</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-01/01_fallo.log</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-01/02_exito.log</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>Expected: false | Received: true</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería rechazar un correo que solo contiene unicauca.edu.co como subcadena | Expected: false | Received: true</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="55" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CU-02</t>
@@ -1212,51 +1255,61 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Registro con correo ya existente</t>
+          <t>Correo ya registrado → HTTP 409 Conflict</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>debería responder 409 si el correo ya existe</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>HTTP 409 Conflict</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Código de estado incorrecto para duplicado</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>return res.status(409) cuando buscarPorCorreo encuentra cuenta</t>
-        </is>
-      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
+          <t>Devolvía 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Usar status 409 cuando el correo existe</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-02/01_fallo.log</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-02/02_exito.log</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 409 | Received: 400</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>● authController.registrar › debería responder 409 si el correo ya existe | Expected: 409 | Received: 400</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CU-03</t>
@@ -1269,51 +1322,61 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Login con cuenta Sin verificar</t>
+          <t>Cuenta Sin verificar → HTTP 403 + EMAIL_NOT_VERIFIED</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>HTTP 403 + codigo EMAIL_NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 401 (confundía con credenciales inválidas)</t>
+          <t>debería responder 403 si el correo no está verificado</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Semántica de autorización incorrecta</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Devolver 403 Forbidden con mensaje de verificación</t>
+          <t>HTTP 403 + EMAIL_NOT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 401</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
+          <t>Se confundía con credenciales inválidas (401)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Devolver 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-03/01_fallo.log</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-03/02_exito.log</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 403 | Received: 401</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>● authController.iniciarSesion › debería responder 403 si el correo no está verificado | Expected: 403 | Received: 401</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CU-04</t>
@@ -1326,51 +1389,61 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>GET /sesion sin encabezado Authorization Bearer</t>
+          <t>Sin Authorization Bearer → HTTP 401</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>debería responder 401 si no hay encabezado Authorization Bearer</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>HTTP 401 Unauthorized</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Falta de autenticación reportada como error de validación</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Responder 401 Debes iniciar sesión</t>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 400</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
+          <t>Falta de auth reportada como 400</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Responder 401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-04/01_fallo.log</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-04/02_exito.log</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 401 | Received: 400</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>● middleware requiereSesion › debería responder 401 si no hay encabezado Authorization Bearer | Expected: 401 | Received: 400</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="55" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CU-05</t>
@@ -1383,51 +1456,61 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Normalización de WhatsApp colombiano</t>
+          <t>Celular CO válido se guarda como +573XXXXXXXXX</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>whatsapp = +573001234567</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>whatsapp = 3001234567 (sin +57)</t>
+          <t>debería normalizar WhatsApp con prefijo 57 a formato \+57</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Incumplía constraint SQL ^\+57[3][0-9]{9}$</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>return `+57${local}` tras validar 10 dígitos</t>
+          <t>whatsapp=+573001234567</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>sin prefijo +57</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
+          <t>Se guardaba sin prefijo internacional</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Prefijar +57 tras validar 10 dígitos</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-05/01_fallo.log</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-05/02_exito.log</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Expected: "+573001234567" | Received: "3001234567"</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería normalizar WhatsApp con prefijo 57 a formato +57 | Expected: "+573001234567" | Received: "3001234567"</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55" customHeight="1">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CU-06</t>
@@ -1440,51 +1523,61 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Verificación con token expirado</t>
+          <t>Token vencido → HTTP 400</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>HTTP 400 + mensaje de expiración</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 404 Not Found</t>
+          <t>debería responder 400 si el enlace expiró</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Token vencido tratado como recurso inexistente</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>status(400) con 'El enlace de verificación expiró.'</t>
+          <t>HTTP 400 expiró</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
+          <t>Respondía 404 Not Found</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>status(400) con mensaje de expiración</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-06/01_fallo.log</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-06/02_exito.log</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 400 | Received: 404</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>● authController.verificar › debería responder 400 si el enlace expiró | Expected: 400 | Received: 404</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="55" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CU-07</t>
@@ -1497,45 +1590,457 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Login con correo/contraseña vacíos</t>
+          <t>Correo/contraseña vacíos → HTTP 400</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>HTTP 401 Unauthorized</t>
+          <t>debería responder 400 si faltan correo o contraseña</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Validación de obligatoriedad mezclada con auth fallida</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Validar presencia antes de consultar BD y responder 400</t>
+          <t>HTTP 400 campos vacíos</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 401</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
+          <t>Respondía 401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Validar presencia y responder 400</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>evidencias/casos-ajuste/CU-07/01_fallo.log</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>evidencias/casos-ajuste/CU-07/02_exito.log</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Expected: 400 | Received: 401</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>● authController.iniciarSesion › debería responder 400 si faltan correo o contraseña | Expected: 400 | Received: 401</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>validation/registro.js</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Contraseña con longitud &lt; 8 → ok=false</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar una contraseña de exactamente 7 caracteres</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>ok=false contraseña 7 chars</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>ok=true (sin mínimo)</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Se omitió la validación de longitud mínima</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Rechazar si contrasena.length &lt; 8</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-08/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-08/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería rechazar una contraseña de exactamente 7 caracteres | Expected: false | Received: true</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>validation/registro.js</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Nombre con longitud &lt; 3 → error en campo nombre</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar un nombre de exactamente 2 caracteres</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>error campo nombre (2 chars)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>nombre aceptado</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>No se validaba el mínimo de 3 caracteres</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Rechazar si nombre.length &lt; 3 || &gt; 120</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-09/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-09/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>● validarRegistro › debería rechazar un nombre de exactamente 2 caracteres | Expected: false | Received: true</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CU-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>controllers/authController.js</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>motivo usado → HTTP 409 Conflict</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 409 si el enlace ya fue usado</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 409 enlace usado</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 400</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Respondía 400 en lugar de conflicto</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>status(409) cuando motivo === 'usado'</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-10/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-10/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>● authController.verificar › debería responder 409 si el enlace ya fue usado | Expected: 409 | Received: 400</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CU-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>controllers/authController.js</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Credenciales inválidas → HTTP 401 genérico</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si la contraseña no coincide</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 401 credenciales</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 404</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Respondía 404 Not Found</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>status(401) con mensaje genérico</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-11/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-11/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>● authController.iniciarSesion › debería responder 401 si la contraseña no coincide | Expected: 401 | Received: 404</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CU-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>middleware/requiereSesion.js</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Token de sesión inválido/expirado → HTTP 401</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si el token de sesión no es válido</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 401 sesión inválida</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>HTTP 403</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Respondía 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>status(401) Tu sesión no es válida o expiró</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-12/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-12/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>● middleware requiereSesion › debería responder 401 si el token de sesión no es válido | Expected: 401 | Received: 403</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CU-13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>middleware/requiereSesion.js</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Solo esquema Bearer es válido; Basic → 401</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar el esquema Basic y exigir Bearer</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Basic → 401 sin consultar</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Basic aceptado como sesión</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Authorization: Basic ... pasaba al buscador de sesión</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Exigir tipo === 'Bearer'</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-13/01_fallo.log</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-13/02_exito.log</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>● middleware requiereSesion › debería rechazar el esquema Basic y exigir Bearer | Expected: 401 | Received: 0</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Resuelto</t>
         </is>
@@ -1552,13 +2057,412 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Criterio de aceptación</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Prueba unitaria asociada</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>CU-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Solo correos que terminen exactamente en @unicauca.edu.co</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar un correo que solo contiene unicauca.edu.co como subcadena</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>CU-02</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Correo ya registrado → HTTP 409 Conflict</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 409 si el correo ya existe</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CU-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta Sin verificar → HTTP 403 + EMAIL_NOT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 403 si el correo no está verificado</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CU-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Sin Authorization Bearer → HTTP 401</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si no hay encabezado Authorization Bearer</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CU-05</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Celular CO válido se guarda como +573XXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>debería normalizar WhatsApp con prefijo 57 a formato \+57</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CU-06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Token vencido → HTTP 400</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 400 si el enlace expiró</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CU-07</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Correo/contraseña vacíos → HTTP 400</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 400 si faltan correo o contraseña</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Contraseña con longitud &lt; 8 → ok=false</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar una contraseña de exactamente 7 caracteres</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Nombre con longitud &lt; 3 → error en campo nombre</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar un nombre de exactamente 2 caracteres</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CU-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>motivo usado → HTTP 409 Conflict</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 409 si el enlace ya fue usado</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CU-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Credenciales inválidas → HTTP 401 genérico</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si la contraseña no coincide</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CU-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Token de sesión inválido/expirado → HTTP 401</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>debería responder 401 si el token de sesión no es válido</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CU-13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Solo esquema Bearer es válido; Basic → 401</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>debería rechazar el esquema Basic y exigir Bearer</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1608,7 +2512,7 @@
 expect(received).toBe(expected) // Object.is equality
 expect(resultado.ok).toBe(false);
 expect(resultado.errores[0].campo).toBe("correo");
-Tests:       1 failed, 7 skipped, 8 total
+Tests:       1 failed, 9 skipped, 10 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1631,7 +2535,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Tests:       7 skipped, 1 passed, 8 total
+          <t>Tests:       9 skipped, 1 passed, 10 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1661,7 +2565,7 @@
 expect(received).toBe(expected) // Object.is equality
 expect(res.statusCode).toBe(409);
 expect(res.cuerpo.mensaje).toMatch(/Ya existe/);
-Tests:       1 failed, 15 skipped, 16 total
+Tests:       1 failed, 16 skipped, 17 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1684,7 +2588,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Tests:       15 skipped, 1 passed, 16 total
+          <t>Tests:       16 skipped, 1 passed, 17 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1715,7 +2619,7 @@
 expect(res.statusCode).toBe(403);
 expect(res.cuerpo.codigo).toBe("EMAIL_NOT_VERIFIED");
 expect(crearSesion).not.toHaveBeenCalled();
-Tests:       1 failed, 15 skipped, 16 total
+Tests:       1 failed, 16 skipped, 17 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1738,7 +2642,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Tests:       15 skipped, 1 passed, 16 total
+          <t>Tests:       16 skipped, 1 passed, 17 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1769,7 +2673,7 @@
 expect(res.statusCode).toBe(401);
 expect(res.cuerpo.mensaje).toMatch(/iniciar sesión/);
 expect(next).not.toHaveBeenCalled();
-Tests:       1 failed, 3 skipped, 4 total
+Tests:       1 failed, 4 skipped, 5 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1792,7 +2696,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Tests:       3 skipped, 1 passed, 4 total
+          <t>Tests:       4 skipped, 1 passed, 5 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1822,7 +2726,7 @@
 expect(received).toBe(expected) // Object.is equality
 expect(resultado.ok).toBe(true);
 expect(resultado.datos.whatsapp).toBe("+573001234567");
-Tests:       1 failed, 7 skipped, 8 total
+Tests:       1 failed, 9 skipped, 10 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1845,7 +2749,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Tests:       7 skipped, 1 passed, 8 total
+          <t>Tests:       9 skipped, 1 passed, 10 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1875,7 +2779,7 @@
 expect(received).toBe(expected) // Object.is equality
 expect(res.statusCode).toBe(400);
 expect(res.cuerpo.mensaje).toMatch(/expiró/);
-Tests:       1 failed, 15 skipped, 16 total
+Tests:       1 failed, 16 skipped, 17 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1898,7 +2802,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Tests:       15 skipped, 1 passed, 16 total
+          <t>Tests:       16 skipped, 1 passed, 17 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1927,7 +2831,7 @@
 Received: 401
 expect(received).toBe(expected) // Object.is equality
 expect(res.statusCode).toBe(400);
-Tests:       1 failed, 15 skipped, 16 total
+Tests:       1 failed, 16 skipped, 17 total
 Test Suites: 1 failed, 1 total</t>
         </is>
       </c>
@@ -1950,7 +2854,327 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Tests:       15 skipped, 1 passed, 16 total
+          <t>Tests:       16 skipped, 1 passed, 17 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/validation/registro.test.js
+● validarRegistro › debería rechazar una contraseña de exactamente 7 caracteres
+Expected: false
+Received: true
+expect(received).toBe(expected) // Object.is equality
+expect(resultado.ok).toBe(false);
+expect(resultado.errores.some((e) =&gt; e.campo === "contrasena")).toBe(true);
+Tests:       1 failed, 9 skipped, 10 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CU-08</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       9 skipped, 1 passed, 10 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/validation/registro.test.js
+● validarRegistro › debería rechazar un nombre de exactamente 2 caracteres
+Expected: false
+Received: true
+expect(received).toBe(expected) // Object.is equality
+expect(resultado.ok).toBe(false);
+expect(resultado.errores[0].campo).toBe("nombre");
+Tests:       1 failed, 9 skipped, 10 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CU-09</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       9 skipped, 1 passed, 10 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CU-10</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/controllers/authController.test.js
+● authController.verificar › debería responder 409 si el enlace ya fue usado
+Expected: 409
+Received: 400
+expect(received).toBe(expected) // Object.is equality
+expect(res.statusCode).toBe(409);
+Tests:       1 failed, 16 skipped, 17 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>CU-10</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       16 skipped, 1 passed, 17 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CU-11</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/controllers/authController.test.js
+● authController.iniciarSesion › debería responder 401 si la contraseña no coincide
+Expected: 401
+Received: 404
+expect(received).toBe(expected) // Object.is equality
+expect(res.statusCode).toBe(401);
+expect(res.cuerpo.mensaje).toBe("Correo o contraseña incorrectos");
+expect(crearSesion).not.toHaveBeenCalled();
+Tests:       1 failed, 16 skipped, 17 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CU-11</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       16 skipped, 1 passed, 17 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>CU-12</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/middleware/requiereSesion.test.js
+● middleware requiereSesion › debería responder 401 si el token de sesión no es válido
+Expected: 401
+Received: 403
+expect(received).toBe(expected) // Object.is equality
+expect(res.statusCode).toBe(401);
+expect(res.cuerpo.mensaje).toMatch(/no es válida|expiró/);
+expect(next).not.toHaveBeenCalled();
+Tests:       1 failed, 4 skipped, 5 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>CU-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       4 skipped, 1 passed, 5 total
+Test Suites: 1 passed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CU-13</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Fallo (antes del ajuste)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>≠0</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>FAIL tests/middleware/requiereSesion.test.js
+● middleware requiereSesion › debería rechazar el esquema Basic y exigir Bearer
+Expected: 401
+Received: 0
+expect(received).toBe(expected) // Object.is equality
+expect(res.statusCode).toBe(401);
+expect(buscarUsuarioPorSesion).not.toHaveBeenCalled();
+expect(next).not.toHaveBeenCalled();
+Tests:       1 failed, 4 skipped, 5 total
+Test Suites: 1 failed, 1 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>CU-13</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Éxito (después del ajuste)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Tests:       4 skipped, 1 passed, 5 total
 Test Suites: 1 passed, 1 total</t>
         </is>
       </c>
@@ -1960,7 +3184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2259,7 +3483,205 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Mapa rápido: dónde están las funciones de prueba</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Carpeta / archivo</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Qué contiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Carpeta raíz de la suite Jest (NO modificar producción desde aquí)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/validation/registro.test.js</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Tests de validarRegistro()</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/security/password.test.js</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Tests de hash/compare bcrypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/models/usuario.test.js</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Tests del modelo usuario (tokens, verificarCuenta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/models/sesion.test.js</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Tests del modelo sesión</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/services/correo.test.js</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tests de enlaceVerificacion / enviarCorreoVerificacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/controllers/authController.test.js</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Tests de registrar / verificar / iniciarSesion / sesionActual</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/middleware/requiereSesion.test.js</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Tests del middleware requiereSesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/routes/authRoutes.test.js</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Tests HTTP Supertest de /api/auth</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>backend/tests/helpers/http.js</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Helpers crearRespuestaMock y crearRequest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/casos-ajuste/CU-XX/</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Evidencia fallo/éxito de cada caso de ajuste</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/Pruebas_Unitarias_RideU.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Este Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>evidencias/MAPA_PRUEBAS.md</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Documentación ampliada del mapa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2268,7 +3690,7 @@
   <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2282,42 +3704,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Mostrar la hoja 'Inventario de pruebas': qué se probó en auth (validación, hash, tokens, controladores, rutas).</t>
+          <t>1. Hoja 'Inventario de pruebas': qué se probó en auth.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Abrir 'Casos de ajuste (7)': cada fila es un defecto detectado por un test unitario.</t>
+          <t>2. Hoja 'Casos de ajuste (13)': cada fila = defecto + criterio + test + evidencias.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. Para cada CU-0X, abrir evidencias/casos-ajuste/CU-0X/01_fallo.log (Expected vs Received) y 02_exito.log (PASS).</t>
+          <t>3. Hoja 'Criterios vs pruebas': trazabilidad criterio ↔ test.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. Mostrar cobertura final (&gt;=70% en lógica de negocio; global ~94% líneas).</t>
+          <t>4. Por cada CU-XX abrir evidencias/casos-ajuste/CU-XX/01_fallo.log y 02_exito.log.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. Comando de reproducción: cd backend &amp;&amp; npm test &amp;&amp; npm run test:coverage</t>
+          <t>5. Hoja 'Ubicación de tests' o MAPA_PRUEBAS.md: dónde están los archivos.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6. Las pruebas usan mocks: no requieren PostgreSQL ni SMTP reales.</t>
+          <t>6. Reproducir: cd backend &amp;&amp; npm test &amp;&amp; npm run test:coverage</t>
         </is>
       </c>
     </row>
